--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>111199387</v>
       </c>
       <c r="B2" t="n">
-        <v>57153</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605531.0823165845</v>
+        <v>605531</v>
       </c>
       <c r="R2" t="n">
-        <v>6553224.871659343</v>
+        <v>6553225</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,19 +748,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,109 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135532371</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103908</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djurgården NNO om , Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>605724</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6553279</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111199387</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,8 +893,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135532371</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135532371</v>
       </c>
       <c r="B3" t="n">
-        <v>103908</v>
+        <v>103959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135532371</v>
       </c>
       <c r="B3" t="n">
-        <v>103959</v>
+        <v>103986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135532371</v>
       </c>
       <c r="B3" t="n">
-        <v>103986</v>
+        <v>103991</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135532371</v>
       </c>
       <c r="B3" t="n">
-        <v>103991</v>
+        <v>103993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135532371</v>
       </c>
       <c r="B3" t="n">
-        <v>103993</v>
+        <v>104013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55092-2021 artfynd.xlsx
+++ b/artfynd/A 55092-2021 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135532371</v>
       </c>
       <c r="B3" t="n">
-        <v>104013</v>
+        <v>104015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
